--- a/logs/user_activity.xlsx
+++ b/logs/user_activity.xlsx
@@ -438,13 +438,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -3313,6 +3313,64 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>13:20:51</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Ctaftelanee</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>ctaftelaneebusinesses@gmail.com</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Chrome</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
